--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2015_T1_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2015_T1_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>94</t>
+    <t>90</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.785</t>
-  </si>
-  <si>
-    <t>(0.091)</t>
-  </si>
-  <si>
-    <t>5.021</t>
-  </si>
-  <si>
-    <t>(0.564)</t>
-  </si>
-  <si>
-    <t>16.548</t>
-  </si>
-  <si>
-    <t>(3.141)</t>
-  </si>
-  <si>
-    <t>21.489</t>
-  </si>
-  <si>
-    <t>(3.793)</t>
-  </si>
-  <si>
-    <t>1.535</t>
-  </si>
-  <si>
-    <t>(0.243)</t>
-  </si>
-  <si>
-    <t>7.138</t>
-  </si>
-  <si>
-    <t>(0.712)</t>
-  </si>
-  <si>
-    <t>1.795</t>
-  </si>
-  <si>
-    <t>(0.493)</t>
-  </si>
-  <si>
-    <t>0.826</t>
-  </si>
-  <si>
-    <t>(0.240)</t>
-  </si>
-  <si>
-    <t>26.099</t>
-  </si>
-  <si>
-    <t>(3.750)</t>
-  </si>
-  <si>
-    <t>17.846</t>
-  </si>
-  <si>
-    <t>(4.485)</t>
+    <t>0.820</t>
+  </si>
+  <si>
+    <t>(0.093)</t>
+  </si>
+  <si>
+    <t>5.244</t>
+  </si>
+  <si>
+    <t>(0.578)</t>
+  </si>
+  <si>
+    <t>14.261</t>
+  </si>
+  <si>
+    <t>(1.965)</t>
+  </si>
+  <si>
+    <t>18.574</t>
+  </si>
+  <si>
+    <t>(2.282)</t>
+  </si>
+  <si>
+    <t>1.440</t>
+  </si>
+  <si>
+    <t>(0.204)</t>
+  </si>
+  <si>
+    <t>7.444</t>
+  </si>
+  <si>
+    <t>(0.727)</t>
+  </si>
+  <si>
+    <t>1.372</t>
+  </si>
+  <si>
+    <t>(0.198)</t>
+  </si>
+  <si>
+    <t>0.681</t>
+  </si>
+  <si>
+    <t>(0.191)</t>
+  </si>
+  <si>
+    <t>23.928</t>
+  </si>
+  <si>
+    <t>(2.927)</t>
+  </si>
+  <si>
+    <t>13.816</t>
+  </si>
+  <si>
+    <t>(1.898)</t>
   </si>
   <si>
     <t>20</t>
@@ -198,7 +198,7 @@
     <t>(11.028)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.598**</t>
-  </si>
-  <si>
-    <t>-0.371</t>
-  </si>
-  <si>
-    <t>40.204***</t>
-  </si>
-  <si>
-    <t>41.305***</t>
-  </si>
-  <si>
-    <t>0.100</t>
-  </si>
-  <si>
-    <t>-1.838</t>
-  </si>
-  <si>
-    <t>0.392</t>
-  </si>
-  <si>
-    <t>0.010</t>
-  </si>
-  <si>
-    <t>52.299***</t>
-  </si>
-  <si>
-    <t>30.047***</t>
+    <t>0.563*</t>
+  </si>
+  <si>
+    <t>-0.594</t>
+  </si>
+  <si>
+    <t>42.492***</t>
+  </si>
+  <si>
+    <t>44.220***</t>
+  </si>
+  <si>
+    <t>0.196</t>
+  </si>
+  <si>
+    <t>-2.144</t>
+  </si>
+  <si>
+    <t>0.815*</t>
+  </si>
+  <si>
+    <t>0.155</t>
+  </si>
+  <si>
+    <t>54.470***</t>
+  </si>
+  <si>
+    <t>34.077***</t>
   </si>
 </sst>
 </file>
